--- a/vse-loti/341042419/spec-341042419.xlsx
+++ b/vse-loti/341042419/spec-341042419.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F2" s="4" t="n">
@@ -553,10 +553,10 @@
         <v>208552.8</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>84708.69</v>
+        <v>84694.92999999999</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>101650.43</v>
+        <v>101633.92</v>
       </c>
     </row>
     <row r="3">
@@ -578,7 +578,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F3" s="4" t="n">
@@ -588,10 +588,10 @@
         <v>21277.2</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>72867.12</v>
+        <v>72937.06</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>87440.55</v>
+        <v>87524.48</v>
       </c>
     </row>
     <row r="4">
@@ -613,7 +613,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F4" s="4" t="n">
@@ -623,10 +623,10 @@
         <v>32958.24</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>86961.06</v>
+        <v>86860.22</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>104353.27</v>
+        <v>104232.26</v>
       </c>
     </row>
     <row r="5">
@@ -648,7 +648,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
@@ -683,7 +683,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F6" s="4" t="n">
@@ -693,10 +693,10 @@
         <v>90090.48</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>81751.8</v>
+        <v>81745.86</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>98102.16</v>
+        <v>98095.03</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F7" s="4" t="n">
@@ -728,10 +728,10 @@
         <v>49553.64</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>78656.57000000001</v>
+        <v>78611.64999999999</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>94387.89</v>
+        <v>94333.98</v>
       </c>
     </row>
     <row r="8">
@@ -753,7 +753,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
@@ -763,10 +763,10 @@
         <v>12663</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>90450</v>
+        <v>90558.02</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>108540</v>
+        <v>108669.63</v>
       </c>
     </row>
     <row r="9">
@@ -788,7 +788,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
@@ -798,10 +798,10 @@
         <v>203019</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>87170.03</v>
+        <v>87180.50999999999</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>104604.04</v>
+        <v>104616.61</v>
       </c>
     </row>
     <row r="10">
@@ -823,7 +823,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
@@ -833,10 +833,10 @@
         <v>307179.6</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>81221.47</v>
+        <v>81212.88</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>97465.75999999999</v>
+        <v>97455.46000000001</v>
       </c>
     </row>
     <row r="11">
@@ -858,7 +858,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
@@ -868,10 +868,10 @@
         <v>29509.2</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>85286.71000000001</v>
+        <v>85385.42</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>102344.05</v>
+        <v>102462.5</v>
       </c>
     </row>
     <row r="12">
@@ -893,7 +893,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
@@ -903,10 +903,10 @@
         <v>140534.16</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>81753.44</v>
+        <v>81770.56</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>98104.13</v>
+        <v>98124.67999999999</v>
       </c>
     </row>
     <row r="13">
@@ -928,7 +928,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Погонный метр</t>
+          <t>м</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -938,10 +938,10 @@
         <v>193655.28</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>84088.27</v>
+        <v>84104.34</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>100905.92</v>
+        <v>100925.2</v>
       </c>
     </row>
     <row r="14">
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>1819255</v>
+        <v>1819255.8</v>
       </c>
     </row>
     <row r="17">

--- a/vse-loti/341042419/spec-341042419.xlsx
+++ b/vse-loti/341042419/spec-341042419.xlsx
@@ -83,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +95,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -463,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,13 +553,13 @@
         <v>2.462</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>208552.8</v>
+        <v>170944.92</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>84694.92999999999</v>
+        <v>69422.03</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>101633.92</v>
+        <v>84694.87</v>
       </c>
     </row>
     <row r="3">
@@ -585,13 +588,13 @@
         <v>0.292</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>21277.2</v>
+        <v>17440.33</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>72937.06</v>
+        <v>59783.22</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>87524.48</v>
+        <v>72935.52</v>
       </c>
     </row>
     <row r="4">
@@ -620,13 +623,13 @@
         <v>0.379</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>32958.24</v>
+        <v>27014.95</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>86860.22</v>
+        <v>71198.92</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>104232.26</v>
+        <v>86862.69</v>
       </c>
     </row>
     <row r="5">
@@ -655,13 +658,13 @@
         <v>4.116</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>530263.2</v>
+        <v>434641.97</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>128829.74</v>
+        <v>105598.25</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>154595.69</v>
+        <v>128829.87</v>
       </c>
     </row>
     <row r="6">
@@ -690,13 +693,13 @@
         <v>1.102</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>90090.48</v>
+        <v>73844.66</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>81745.86</v>
+        <v>67004.78999999999</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>98095.03</v>
+        <v>81745.84</v>
       </c>
     </row>
     <row r="7">
@@ -725,13 +728,13 @@
         <v>0.63</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>49553.64</v>
+        <v>40617.74</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>78611.64999999999</v>
+        <v>64436.89</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>94333.98</v>
+        <v>78613.00999999999</v>
       </c>
     </row>
     <row r="8">
@@ -760,13 +763,13 @@
         <v>0.14</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>12663</v>
+        <v>10379.51</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>90558.02</v>
+        <v>74226.67999999999</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>108669.63</v>
+        <v>90556.56</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +798,13 @@
         <v>2.329</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>203019</v>
+        <v>166409.02</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>87180.50999999999</v>
+        <v>71460.06</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>104616.61</v>
+        <v>87181.28</v>
       </c>
     </row>
     <row r="10">
@@ -830,13 +833,13 @@
         <v>3.782</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>307179.6</v>
+        <v>251786.56</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>81212.88</v>
+        <v>66567.89</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>97455.46000000001</v>
+        <v>81212.83</v>
       </c>
     </row>
     <row r="11">
@@ -865,13 +868,13 @@
         <v>0.346</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>29509.2</v>
+        <v>24187.87</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>85385.42</v>
+        <v>69986.98</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>102462.5</v>
+        <v>85384.11</v>
       </c>
     </row>
     <row r="12">
@@ -900,13 +903,13 @@
         <v>1.719</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>140534.16</v>
+        <v>115191.93</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>81770.56</v>
+        <v>67025.97</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>98124.67999999999</v>
+        <v>81771.69</v>
       </c>
     </row>
     <row r="13">
@@ -935,13 +938,13 @@
         <v>2.303</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>193655.28</v>
+        <v>158733.84</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>84104.34</v>
+        <v>68937.67</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>100925.2</v>
+        <v>84103.96000000001</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +957,7 @@
         <v>19.6</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>1819255.8</v>
+        <v>1491193.3</v>
       </c>
     </row>
     <row r="15">
@@ -964,22 +967,39 @@
         </is>
       </c>
       <c r="G15" s="8" t="n">
+        <v>1491193.28</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
         <v>1819255.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; по ч. 1 ст. 22 44-ФЗ цена контракта включает налоги, поэтому сумма документа принята как цена с НДС. «с НДС» — сумма из документа, «без НДС» = сумма ÷ 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
           <t>Источник: Извещение о проведении запроса котировок в электронной форме от 18.09.2026 №0848300016526000392.htm
 Приложение 5 к Контракту.docx</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:B19"/>
+    <mergeCell ref="A19:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341042419/spec-341042419.xlsx
+++ b/vse-loti/341042419/spec-341042419.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -513,17 +514,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -553,13 +559,16 @@
         <v>2.462</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>69422.03</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>170944.92</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>69422.03</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>84694.87</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>208552.8</v>
       </c>
     </row>
     <row r="3">
@@ -588,13 +597,16 @@
         <v>0.292</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>59783.22</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>17440.33</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>59783.22</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>72935.52</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>21277.2</v>
       </c>
     </row>
     <row r="4">
@@ -623,13 +635,16 @@
         <v>0.379</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>71198.92</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>27014.95</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>71198.92</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>86862.69</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>32958.24</v>
       </c>
     </row>
     <row r="5">
@@ -658,13 +673,16 @@
         <v>4.116</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>105598.25</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>434641.97</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>105598.25</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>128829.87</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>530263.2</v>
       </c>
     </row>
     <row r="6">
@@ -693,13 +711,16 @@
         <v>1.102</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>67004.78999999999</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>73844.66</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>67004.78999999999</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>81745.84</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>90090.49000000001</v>
       </c>
     </row>
     <row r="7">
@@ -728,13 +749,16 @@
         <v>0.63</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>64436.89</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>40617.74</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>64436.89</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>78613.00999999999</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>49553.64</v>
       </c>
     </row>
     <row r="8">
@@ -763,13 +787,16 @@
         <v>0.14</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>74226.67999999999</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>10379.51</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>74226.67999999999</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>90556.56</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>12663</v>
       </c>
     </row>
     <row r="9">
@@ -798,13 +825,16 @@
         <v>2.329</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>71460.06</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>166409.02</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>71460.06</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>87181.28</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>203019</v>
       </c>
     </row>
     <row r="10">
@@ -833,13 +863,16 @@
         <v>3.782</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>66567.89</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>251786.56</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>66567.89</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>81212.83</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>307179.6</v>
       </c>
     </row>
     <row r="11">
@@ -868,13 +901,16 @@
         <v>0.346</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>69986.98</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>24187.87</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>69986.98</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>85384.11</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>29509.2</v>
       </c>
     </row>
     <row r="12">
@@ -903,13 +939,16 @@
         <v>1.719</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>67025.97</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>115191.93</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>67025.97</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>81771.69</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>140534.15</v>
       </c>
     </row>
     <row r="13">
@@ -938,14 +977,17 @@
         <v>2.303</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>68937.67</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>158733.84</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>68937.67</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>84103.96000000001</v>
       </c>
+      <c r="J13" s="5" t="n">
+        <v>193655.28</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -957,7 +999,16 @@
         <v>19.6</v>
       </c>
       <c r="G14" s="8" t="n">
+        <v>76081.28999999999</v>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>1491193.3</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>92819.17</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>1819255.83</v>
       </c>
     </row>
     <row r="15">
@@ -966,7 +1017,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="H15" s="8" t="n">
         <v>1491193.28</v>
       </c>
     </row>
@@ -976,7 +1027,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="J16" s="8" t="n">
         <v>1819255.8</v>
       </c>
     </row>
